--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2221,6 +2221,838 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127458256</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>549871</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6984834</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127458175</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>549926</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6984784</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rik förekomst, ca 2 kvadratmeter.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127458215</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>549911</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6984814</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127458178</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>549926</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6984784</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127458284</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>549865</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6984842</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127458254</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98464</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>549871</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6984834</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127458313</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>549834</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6984825</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127458294</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>549834</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6984825</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>127458256</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>127458175</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127458215</v>
       </c>
       <c r="B17" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127458178</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>127458284</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127458254</v>
+        <v>127458313</v>
       </c>
       <c r="B20" t="n">
-        <v>98464</v>
+        <v>92620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,27 +2757,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2785,10 +2784,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549871</v>
+        <v>549834</v>
       </c>
       <c r="R20" t="n">
-        <v>6984834</v>
+        <v>6984825</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2821,6 +2820,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127458313</v>
+        <v>127458254</v>
       </c>
       <c r="B21" t="n">
-        <v>92616</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2859,26 +2863,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549834</v>
+        <v>549871</v>
       </c>
       <c r="R21" t="n">
-        <v>6984825</v>
+        <v>6984834</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,11 +2927,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,7 +2957,7 @@
         <v>127458294</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>127458256</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>127458175</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>127458284</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127458313</v>
+        <v>127458254</v>
       </c>
       <c r="B20" t="n">
-        <v>92620</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,26 +2757,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2784,10 +2785,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549834</v>
+        <v>549871</v>
       </c>
       <c r="R20" t="n">
-        <v>6984825</v>
+        <v>6984834</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2820,11 +2821,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2848,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127458254</v>
+        <v>127458313</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>92620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,27 +2859,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549871</v>
+        <v>549834</v>
       </c>
       <c r="R21" t="n">
-        <v>6984834</v>
+        <v>6984825</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2927,6 +2922,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2746,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127458254</v>
+        <v>127458313</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>92620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,27 +2757,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2785,10 +2784,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549871</v>
+        <v>549834</v>
       </c>
       <c r="R20" t="n">
-        <v>6984834</v>
+        <v>6984825</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2821,6 +2820,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127458313</v>
+        <v>127458254</v>
       </c>
       <c r="B21" t="n">
-        <v>92620</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2859,26 +2863,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549834</v>
+        <v>549871</v>
       </c>
       <c r="R21" t="n">
-        <v>6984825</v>
+        <v>6984834</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,11 +2927,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>127458256</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>127458175</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127458215</v>
       </c>
       <c r="B17" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127458178</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>127458284</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>127458313</v>
       </c>
       <c r="B20" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>127458254</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>127458294</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2746,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127458313</v>
+        <v>127458254</v>
       </c>
       <c r="B20" t="n">
-        <v>92622</v>
+        <v>98471</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,26 +2757,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2784,10 +2785,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549834</v>
+        <v>549871</v>
       </c>
       <c r="R20" t="n">
-        <v>6984825</v>
+        <v>6984834</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2820,11 +2821,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2848,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127458254</v>
+        <v>127458313</v>
       </c>
       <c r="B21" t="n">
-        <v>98471</v>
+        <v>92622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,27 +2859,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549871</v>
+        <v>549834</v>
       </c>
       <c r="R21" t="n">
-        <v>6984834</v>
+        <v>6984825</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2927,6 +2922,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>127458256</v>
       </c>
       <c r="B15" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>127458175</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>127458284</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>127458254</v>
       </c>
       <c r="B20" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>127458313</v>
       </c>
       <c r="B21" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>127458256</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>127458175</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127458215</v>
       </c>
       <c r="B17" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127458178</v>
       </c>
       <c r="B18" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>127458284</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>127458254</v>
       </c>
       <c r="B20" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>127458313</v>
       </c>
       <c r="B21" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>127458294</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>127458256</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>127458175</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127458215</v>
       </c>
       <c r="B17" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127458178</v>
       </c>
       <c r="B18" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>127458284</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>127458254</v>
       </c>
       <c r="B20" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>127458313</v>
       </c>
       <c r="B21" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>127458294</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>127458256</v>
       </c>
       <c r="B15" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>127458175</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>127458284</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>127458254</v>
       </c>
       <c r="B20" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>127458313</v>
       </c>
       <c r="B21" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2226,7 +2226,7 @@
         <v>127458256</v>
       </c>
       <c r="B15" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>127458175</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>127458284</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>127458254</v>
       </c>
       <c r="B20" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>127458313</v>
       </c>
       <c r="B21" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,6 +3053,738 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128268568</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92646</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>549800</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6984875</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128268603</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92674</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>549977</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6984739</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128268552</v>
+      </c>
+      <c r="B25" t="n">
+        <v>88624</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>549632</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6984870</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128268544</v>
+      </c>
+      <c r="B26" t="n">
+        <v>86764</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>549735</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6984767</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128268593</v>
+      </c>
+      <c r="B27" t="n">
+        <v>88624</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>549854</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6984830</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128268547</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90914</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>937</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vit vedfingersvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lentaria epichnoa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>549735</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6984767</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På grov asplåga.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Grov asplåga.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Populus tremula # Grov asplåga.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128268594</v>
+      </c>
+      <c r="B29" t="n">
+        <v>88624</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>550013</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6984854</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>127458256</v>
       </c>
       <c r="B15" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>127458175</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>127458284</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>127458254</v>
       </c>
       <c r="B20" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>127458313</v>
       </c>
       <c r="B21" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B24" t="n">
-        <v>92674</v>
+        <v>88624</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R24" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B25" t="n">
-        <v>88624</v>
+        <v>92674</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R25" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -2746,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127458254</v>
+        <v>127458313</v>
       </c>
       <c r="B20" t="n">
-        <v>98491</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,27 +2757,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2785,10 +2784,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549871</v>
+        <v>549834</v>
       </c>
       <c r="R20" t="n">
-        <v>6984834</v>
+        <v>6984825</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2821,6 +2820,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127458313</v>
+        <v>127458254</v>
       </c>
       <c r="B21" t="n">
-        <v>92642</v>
+        <v>98491</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2859,26 +2863,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549834</v>
+        <v>549871</v>
       </c>
       <c r="R21" t="n">
-        <v>6984825</v>
+        <v>6984834</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,11 +2927,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,10 +3156,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>88624</v>
+        <v>92674</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R24" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>92674</v>
+        <v>88624</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R25" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92646</v>
+        <v>92654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B24" t="n">
-        <v>92674</v>
+        <v>88630</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R24" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B25" t="n">
-        <v>88624</v>
+        <v>92682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R25" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3361,7 +3361,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86764</v>
+        <v>86768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88624</v>
+        <v>88630</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>90914</v>
+        <v>90920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88624</v>
+        <v>88630</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92654</v>
+        <v>92746</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>88630</v>
+        <v>92774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R24" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>92682</v>
+        <v>88722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R25" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3361,7 +3361,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86768</v>
+        <v>86860</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88630</v>
+        <v>88722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>90920</v>
+        <v>91012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88630</v>
+        <v>88722</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3156,10 +3156,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B24" t="n">
-        <v>92774</v>
+        <v>88722</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R24" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B25" t="n">
-        <v>88722</v>
+        <v>92774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R25" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,14 +3152,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>88722</v>
+        <v>92786</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,21 +3171,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R24" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3253,14 +3257,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>92774</v>
+        <v>88734</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R25" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3354,14 +3362,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86860</v>
+        <v>86870</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3455,14 +3467,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88722</v>
+        <v>88734</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,14 +3572,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>91024</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3682,14 +3702,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88722</v>
+        <v>88734</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,7 +3807,11 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>92786</v>
+        <v>92788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>88734</v>
+        <v>88736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86870</v>
+        <v>86872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88734</v>
+        <v>88736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91024</v>
+        <v>91026</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88734</v>
+        <v>88736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>92788</v>
+        <v>92789</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91026</v>
+        <v>91027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>92789</v>
+        <v>92816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>88736</v>
+        <v>88763</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86872</v>
+        <v>86899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88736</v>
+        <v>88763</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91027</v>
+        <v>91054</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88736</v>
+        <v>88763</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>88763</v>
+        <v>88767</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86899</v>
+        <v>86903</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88763</v>
+        <v>88767</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91054</v>
+        <v>91059</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88763</v>
+        <v>88767</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>92821</v>
+        <v>92828</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>88767</v>
+        <v>88768</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86903</v>
+        <v>86904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88767</v>
+        <v>88768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91059</v>
+        <v>91064</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88767</v>
+        <v>88768</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B24" t="n">
-        <v>92828</v>
+        <v>88772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R24" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B25" t="n">
-        <v>88768</v>
+        <v>92832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R25" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3373,7 +3373,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86904</v>
+        <v>86908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88768</v>
+        <v>88772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91064</v>
+        <v>91068</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88768</v>
+        <v>88772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>88772</v>
+        <v>92837</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R24" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>92832</v>
+        <v>88777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R25" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3373,7 +3373,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86908</v>
+        <v>86913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88772</v>
+        <v>88777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91068</v>
+        <v>91073</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88772</v>
+        <v>88777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B24" t="n">
-        <v>92845</v>
+        <v>88787</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R24" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B25" t="n">
-        <v>88784</v>
+        <v>92850</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R25" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3373,7 +3373,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86920</v>
+        <v>86923</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88784</v>
+        <v>88787</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91080</v>
+        <v>91083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88784</v>
+        <v>88787</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>88787</v>
+        <v>92853</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R24" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>92850</v>
+        <v>88790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R25" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3373,7 +3373,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86923</v>
+        <v>86926</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88787</v>
+        <v>88790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91083</v>
+        <v>91086</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88787</v>
+        <v>88790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B24" t="n">
-        <v>92853</v>
+        <v>88790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R24" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B25" t="n">
-        <v>88790</v>
+        <v>92853</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R25" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128268568</v>
       </c>
       <c r="B23" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268552</v>
+        <v>128268603</v>
       </c>
       <c r="B24" t="n">
-        <v>88790</v>
+        <v>92860</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549632</v>
+        <v>549977</v>
       </c>
       <c r="R24" t="n">
-        <v>6984870</v>
+        <v>6984739</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268603</v>
+        <v>128268552</v>
       </c>
       <c r="B25" t="n">
-        <v>92853</v>
+        <v>88794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549977</v>
+        <v>549632</v>
       </c>
       <c r="R25" t="n">
-        <v>6984739</v>
+        <v>6984870</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3373,7 +3373,7 @@
         <v>128268544</v>
       </c>
       <c r="B26" t="n">
-        <v>86926</v>
+        <v>86930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128268593</v>
       </c>
       <c r="B27" t="n">
-        <v>88790</v>
+        <v>88794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>128268547</v>
       </c>
       <c r="B28" t="n">
-        <v>91086</v>
+        <v>91090</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128268594</v>
       </c>
       <c r="B29" t="n">
-        <v>88790</v>
+        <v>88794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104020621</v>
+        <v>104020655</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549832.4104125458</v>
+        <v>549514</v>
       </c>
       <c r="R2" t="n">
-        <v>6984971.436252741</v>
+        <v>6984879</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,53 +791,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104020626</v>
+        <v>128268547</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>937</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eberhålet, Jmt</t>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549556.5441906105</v>
+        <v>549735</v>
       </c>
       <c r="R3" t="n">
-        <v>6984821.755282758</v>
+        <v>6984767</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +859,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,12 +878,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Grov asplåga.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula # Grov asplåga.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -906,26 +910,21 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104020655</v>
+        <v>111309373</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,34 +932,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eberhålet, Jmt</t>
+          <t>Sönnerstmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549513.7871550655</v>
+        <v>550022</v>
       </c>
       <c r="R4" t="n">
-        <v>6984879.295289483</v>
+        <v>6984866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +987,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,11 +1003,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1027,61 +1012,55 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104020669</v>
+        <v>111391843</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eberhålet, Jmt</t>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549546.3928677853</v>
+        <v>549948</v>
       </c>
       <c r="R5" t="n">
-        <v>6984830.693165033</v>
+        <v>6984922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,22 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,13 +1101,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1148,64 +1113,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111391834</v>
+        <v>104020628</v>
       </c>
       <c r="B6" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog väster om Sönnerstmyran, Jmt</t>
+          <t>Eberhålet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549948.3430357982</v>
+        <v>550006</v>
       </c>
       <c r="R6" t="n">
-        <v>6984921.841925205</v>
+        <v>6984734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,27 +1185,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal grov sälg.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,9 +1209,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1273,22 +1225,21 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111391797</v>
+        <v>111391793</v>
       </c>
       <c r="B7" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550008.5227175603</v>
+        <v>550008</v>
       </c>
       <c r="R7" t="n">
-        <v>6984886.396702384</v>
+        <v>6984887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,19 +1307,9 @@
           <t>2023-08-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,15 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111391843</v>
+        <v>128268603</v>
       </c>
       <c r="B8" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,13 +1375,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549948.3430357982</v>
+        <v>549977</v>
       </c>
       <c r="R8" t="n">
-        <v>6984921.841925205</v>
+        <v>6984739</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,22 +1405,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,19 +1434,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111391904</v>
+        <v>111391834</v>
       </c>
       <c r="B9" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1555,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549834.8598072252</v>
+        <v>549948</v>
       </c>
       <c r="R9" t="n">
-        <v>6984960.108837452</v>
+        <v>6984922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,24 +1513,14 @@
           <t>2023-08-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-06</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,15 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111391798</v>
+        <v>127458313</v>
       </c>
       <c r="B10" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1676,13 +1586,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550008.5227175603</v>
+        <v>549834</v>
       </c>
       <c r="R10" t="n">
-        <v>6984886.396702384</v>
+        <v>6984825</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,22 +1616,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,37 +1654,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111391889</v>
+        <v>128268568</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1792,13 +1692,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549881.4435103451</v>
+        <v>549800</v>
       </c>
       <c r="R11" t="n">
-        <v>6984890.813158087</v>
+        <v>6984875</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1822,22 +1722,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,19 +1751,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111391873</v>
+        <v>128268552</v>
       </c>
       <c r="B12" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549881.4435103451</v>
+        <v>549632</v>
       </c>
       <c r="R12" t="n">
-        <v>6984890.813158087</v>
+        <v>6984870</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,27 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På asp.</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,41 +1856,40 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111391793</v>
+        <v>128268593</v>
       </c>
       <c r="B13" t="n">
-        <v>89416</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>4412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2029,13 +1902,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550008.5227175603</v>
+        <v>549854</v>
       </c>
       <c r="R13" t="n">
-        <v>6984886.396702384</v>
+        <v>6984830</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2059,22 +1932,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2098,19 +1961,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111391838</v>
+        <v>128268594</v>
       </c>
       <c r="B14" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2145,13 +2007,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549948.3430357982</v>
+        <v>550013</v>
       </c>
       <c r="R14" t="n">
-        <v>6984921.841925205</v>
+        <v>6984854</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2175,27 +2037,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal grov sälg.</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,42 +2066,45 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127458256</v>
+        <v>128268598</v>
       </c>
       <c r="B15" t="n">
-        <v>98387</v>
+        <v>89156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2262,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549871</v>
+        <v>549917</v>
       </c>
       <c r="R15" t="n">
-        <v>6984834</v>
+        <v>6984746</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2292,12 +2142,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2321,14 +2171,18 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127458175</v>
+        <v>111391889</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,27 +2190,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2364,13 +2217,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549926</v>
+        <v>549882</v>
       </c>
       <c r="R16" t="n">
-        <v>6984784</v>
+        <v>6984891</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2394,17 +2247,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rik förekomst, ca 2 kvadratmeter.</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127458215</v>
+        <v>127458294</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2470,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549911</v>
+        <v>549834</v>
       </c>
       <c r="R17" t="n">
-        <v>6984814</v>
+        <v>6984825</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2506,11 +2354,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,32 +2381,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127458178</v>
+        <v>111391797</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2576,13 +2419,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549926</v>
+        <v>550008</v>
       </c>
       <c r="R18" t="n">
-        <v>6984784</v>
+        <v>6984887</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2606,17 +2449,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,52 +2482,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127458284</v>
+        <v>1959049</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog väster om Sönnerstmyran, Jmt</t>
+          <t>(18G7b20), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549865</v>
+        <v>549559</v>
       </c>
       <c r="R19" t="n">
-        <v>6984842</v>
+        <v>6984849</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2713,12 +2547,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2001-08-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2001-08-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>180671201 / LOB PULM / Enstaka-sparsam (1)  / OBJ.AREA:0,6 ha</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,70 +2566,80 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Lövbränna / Lövrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Gammal grov asp</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Gullik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127458313</v>
+        <v>104020621</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog väster om Sönnerstmyran, Jmt</t>
+          <t>Eberhålet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549834</v>
+        <v>549833</v>
       </c>
       <c r="R20" t="n">
-        <v>6984825</v>
+        <v>6984971</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2814,17 +2663,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar. Vit mycelmatta.</t>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,9 +2687,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2845,45 +2703,48 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127458254</v>
+        <v>111391798</v>
       </c>
       <c r="B21" t="n">
-        <v>98491</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2891,13 +2752,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549871</v>
+        <v>550008</v>
       </c>
       <c r="R21" t="n">
-        <v>6984834</v>
+        <v>6984887</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2921,12 +2782,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2954,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127458294</v>
+        <v>111391838</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2992,13 +2853,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549834</v>
+        <v>549948</v>
       </c>
       <c r="R22" t="n">
-        <v>6984825</v>
+        <v>6984922</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3022,12 +2883,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,32 +2921,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128268568</v>
+        <v>111391873</v>
       </c>
       <c r="B23" t="n">
-        <v>92830</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3093,13 +2959,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549800</v>
+        <v>549882</v>
       </c>
       <c r="R23" t="n">
-        <v>6984875</v>
+        <v>6984891</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3123,12 +2989,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,18 +3023,14 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128268603</v>
+        <v>111391904</v>
       </c>
       <c r="B24" t="n">
-        <v>92860</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,21 +3038,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,13 +3065,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549977</v>
+        <v>549835</v>
       </c>
       <c r="R24" t="n">
-        <v>6984739</v>
+        <v>6984960</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3228,12 +3095,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,18 +3129,14 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128268552</v>
+        <v>127458178</v>
       </c>
       <c r="B25" t="n">
-        <v>88794</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3303,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549632</v>
+        <v>549926</v>
       </c>
       <c r="R25" t="n">
-        <v>6984870</v>
+        <v>6984784</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3333,12 +3201,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,40 +3235,36 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128268544</v>
+        <v>127458215</v>
       </c>
       <c r="B26" t="n">
-        <v>86930</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248955</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3408,10 +3277,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549735</v>
+        <v>549911</v>
       </c>
       <c r="R26" t="n">
-        <v>6984767</v>
+        <v>6984814</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3438,12 +3307,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3467,18 +3341,14 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128268593</v>
+        <v>127458347</v>
       </c>
       <c r="B27" t="n">
-        <v>88794</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,21 +3356,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3513,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549854</v>
+        <v>549520</v>
       </c>
       <c r="R27" t="n">
-        <v>6984830</v>
+        <v>6984930</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3543,12 +3413,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På grov asplåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,18 +3447,14 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128268547</v>
+        <v>111309437</v>
       </c>
       <c r="B28" t="n">
-        <v>91090</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3591,40 +3462,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>937</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skog väster om Sönnerstmyran, Jmt</t>
+          <t>Sönnerstmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549735</v>
+        <v>550022</v>
       </c>
       <c r="R28" t="n">
-        <v>6984767</v>
+        <v>6984866</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3648,17 +3522,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På grov asplåga.</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3667,29 +3536,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Grov asplåga.</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Populus tremula # Grov asplåga.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3702,18 +3550,14 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128268594</v>
+        <v>127458162</v>
       </c>
       <c r="B29" t="n">
-        <v>88794</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,26 +3565,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3748,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550013</v>
+        <v>549984</v>
       </c>
       <c r="R29" t="n">
-        <v>6984854</v>
+        <v>6984732</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3778,12 +3623,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,7 +3642,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3807,7 +3656,1077 @@
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127458256</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>549871</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6984834</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3010112</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>(18G7b20), Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>549559</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6984849</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2001-08-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2001-08-20</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>180671201 / GOOD REP / Tämligen allmän (2)  / OBJ.AREA:0,6 ha</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Lövbränna / Lövrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Gullik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>104020669</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Eberhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>549546</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6984831</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127458175</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>549926</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6984784</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rik förekomst, ca 2 kvadratmeter.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127458284</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>549865</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6984842</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>104020626</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Eberhålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>549557</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6984822</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4344940</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>(18G7b20), Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>549559</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6984849</v>
+      </c>
+      <c r="S36" t="n">
+        <v>50</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2001-08-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2001-08-20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>180671201 / LIST COR / Tämligen allmän (2)  / OBJ.AREA:0,6 ha</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Lövbränna / Lövrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gullik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127458254</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>549871</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6984834</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127458335</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>549541</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6984918</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128268544</v>
+      </c>
+      <c r="B39" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skog väster om Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>549735</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6984767</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -4632,7 +4632,7 @@
         <v>128268544</v>
       </c>
       <c r="B39" t="n">
-        <v>87291</v>
+        <v>87353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020655</t>
         </is>
       </c>
     </row>
@@ -918,6 +928,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128268547</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111309373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111391843</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020628</t>
         </is>
       </c>
     </row>
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111391793</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128268603</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111391834</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458313</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128268568</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1861,6 +1916,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128268552</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128268593</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2071,6 +2136,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128268594</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2176,6 +2246,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128268598</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111391889</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458294</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2479,6 +2564,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111391797</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2595,6 +2685,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1959049</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2709,6 +2804,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020621</t>
         </is>
       </c>
     </row>
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111391798</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2918,6 +3023,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111391838</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3024,6 +3134,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111391873</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3130,6 +3245,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111391904</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3236,6 +3356,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458178</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3342,6 +3467,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458215</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3448,6 +3578,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458347</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111309437</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3657,6 +3797,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458162</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3759,6 +3904,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458256</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3870,6 +4020,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3010112</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3984,6 +4139,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020669</t>
         </is>
       </c>
     </row>
@@ -4093,6 +4253,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458175</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4195,6 +4360,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458284</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4311,6 +4481,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020626</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4420,6 +4595,11 @@
       <c r="AY36" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4344940</t>
         </is>
       </c>
     </row>
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458254</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4626,6 +4811,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127458335</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4731,8 +4921,53 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128268544</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -4822,7 +4822,7 @@
         <v>128268544</v>
       </c>
       <c r="B39" t="n">
-        <v>87353</v>
+        <v>87393</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 41701-2024 artfynd.xlsx
+++ b/artfynd/A 41701-2024 artfynd.xlsx
@@ -4822,7 +4822,7 @@
         <v>128268544</v>
       </c>
       <c r="B39" t="n">
-        <v>87393</v>
+        <v>87420</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
